--- a/excel_routes/route_ATZ_RUH_threats.xlsx
+++ b/excel_routes/route_ATZ_RUH_threats.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_260726_at_14.46\reports\excel_routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_270726_at_12.25\reports\excel_routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{578B4BA9-0E7C-4A51-A20E-9857C3207E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87FF5BD1-1A9F-45A2-A12D-0DF2888DD879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12972" yWindow="348" windowWidth="10068" windowHeight="10284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="51">
   <si>
     <t>Date</t>
   </si>
@@ -66,30 +66,27 @@
     <t>SM-465</t>
   </si>
   <si>
+    <t>Nesma Airlines NE-160</t>
+  </si>
+  <si>
+    <t>MED</t>
+  </si>
+  <si>
+    <t>EGP</t>
+  </si>
+  <si>
+    <t>Nile Air NP-251</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
     <t>Nile Air NP-151</t>
   </si>
   <si>
-    <t>MED</t>
-  </si>
-  <si>
-    <t>EGP</t>
-  </si>
-  <si>
-    <t>Nile Air NP-251</t>
-  </si>
-  <si>
-    <t>Nesma Airlines NE-160</t>
-  </si>
-  <si>
     <t>29-JUL-26</t>
   </si>
   <si>
-    <t>Nesma Airlines NE-162</t>
-  </si>
-  <si>
-    <t>LOW</t>
-  </si>
-  <si>
     <t>Nesma Airlines NE-164</t>
   </si>
   <si>
@@ -102,39 +99,42 @@
     <t>Nile Air NP-353</t>
   </si>
   <si>
-    <t>Nile Air NP-351</t>
-  </si>
-  <si>
     <t>05-AUG-26</t>
   </si>
   <si>
+    <t>Nile Air NP-455</t>
+  </si>
+  <si>
+    <t>11-AUG-26</t>
+  </si>
+  <si>
+    <t>Air Arabia Egypt E5-410</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>Nile Air NP-253</t>
+  </si>
+  <si>
+    <t>12-AUG-26</t>
+  </si>
+  <si>
+    <t>Air Arabia Egypt E5-415</t>
+  </si>
+  <si>
+    <t>18-AUG-26</t>
+  </si>
+  <si>
+    <t>Nile Air NP-255</t>
+  </si>
+  <si>
+    <t>19-AUG-26</t>
+  </si>
+  <si>
     <t>Nile Air NP-453</t>
   </si>
   <si>
-    <t>Nile Air NP-451</t>
-  </si>
-  <si>
-    <t>11-AUG-26</t>
-  </si>
-  <si>
-    <t>Nile Air NP-253</t>
-  </si>
-  <si>
-    <t>12-AUG-26</t>
-  </si>
-  <si>
-    <t>HIGH</t>
-  </si>
-  <si>
-    <t>18-AUG-26</t>
-  </si>
-  <si>
-    <t>Nile Air NP-255</t>
-  </si>
-  <si>
-    <t>19-AUG-26</t>
-  </si>
-  <si>
     <t>25-AUG-26</t>
   </si>
   <si>
@@ -144,13 +144,13 @@
     <t>01-SEP-26</t>
   </si>
   <si>
+    <t>flyadeal F3-614</t>
+  </si>
+  <si>
+    <t>flyadeal F3-608</t>
+  </si>
+  <si>
     <t>flyadeal F3-606</t>
-  </si>
-  <si>
-    <t>flyadeal F3-614</t>
-  </si>
-  <si>
-    <t>flyadeal F3-608</t>
   </si>
   <si>
     <t>02-SEP-26</t>
@@ -583,12 +583,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="6" width="10" customWidth="1"/>
     <col min="7" max="7" width="153.44140625" customWidth="1"/>
@@ -644,13 +644,13 @@
         <v>13</v>
       </c>
       <c r="D2" s="2">
-        <v>13693</v>
+        <v>13870</v>
       </c>
       <c r="E2" s="2">
-        <v>20642</v>
+        <v>20641</v>
       </c>
       <c r="F2" s="2">
-        <v>-6949</v>
+        <v>-6771</v>
       </c>
       <c r="G2" s="2">
         <v>30</v>
@@ -679,13 +679,13 @@
         <v>16</v>
       </c>
       <c r="D3" s="2">
-        <v>13693</v>
+        <v>15809</v>
       </c>
       <c r="E3" s="2">
-        <v>20642</v>
+        <v>20641</v>
       </c>
       <c r="F3" s="2">
-        <v>-6949</v>
+        <v>-4832</v>
       </c>
       <c r="G3" s="2">
         <v>30</v>
@@ -696,8 +696,8 @@
       <c r="I3" s="2">
         <v>0</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>14</v>
+      <c r="J3" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>15</v>
@@ -711,28 +711,28 @@
         <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="2">
+        <v>15809</v>
+      </c>
+      <c r="E4" s="2">
+        <v>20641</v>
+      </c>
+      <c r="F4" s="2">
+        <v>-4832</v>
+      </c>
+      <c r="G4" s="2">
+        <v>30</v>
+      </c>
+      <c r="H4" s="2">
+        <v>30</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="D4" s="2">
-        <v>13870</v>
-      </c>
-      <c r="E4" s="2">
-        <v>20642</v>
-      </c>
-      <c r="F4" s="2">
-        <v>-6772</v>
-      </c>
-      <c r="G4" s="2">
-        <v>30</v>
-      </c>
-      <c r="H4" s="2">
-        <v>30</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>14</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>15</v>
@@ -740,22 +740,22 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2">
-        <v>12464</v>
+        <v>13870</v>
       </c>
       <c r="E5" s="2">
         <v>17447</v>
       </c>
       <c r="F5" s="2">
-        <v>-4983</v>
+        <v>-3577</v>
       </c>
       <c r="G5" s="2">
         <v>30</v>
@@ -767,7 +767,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>15</v>
@@ -775,22 +775,22 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D6" s="2">
-        <v>13693</v>
+        <v>11153</v>
       </c>
       <c r="E6" s="2">
         <v>17447</v>
       </c>
       <c r="F6" s="2">
-        <v>-3754</v>
+        <v>-6294</v>
       </c>
       <c r="G6" s="2">
         <v>30</v>
@@ -801,8 +801,8 @@
       <c r="I6" s="2">
         <v>0</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>20</v>
+      <c r="J6" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>15</v>
@@ -810,22 +810,22 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D7" s="2">
-        <v>13870</v>
+        <v>11153</v>
       </c>
       <c r="E7" s="2">
         <v>17447</v>
       </c>
       <c r="F7" s="2">
-        <v>-3577</v>
+        <v>-6294</v>
       </c>
       <c r="G7" s="2">
         <v>30</v>
@@ -836,8 +836,8 @@
       <c r="I7" s="2">
         <v>0</v>
       </c>
-      <c r="J7" s="4" t="s">
-        <v>20</v>
+      <c r="J7" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>15</v>
@@ -845,13 +845,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D8" s="2">
         <v>11153</v>
@@ -880,13 +880,13 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D9" s="2">
         <v>11153</v>
@@ -915,13 +915,13 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D10" s="2">
         <v>11153</v>
@@ -950,13 +950,13 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D11" s="2">
         <v>11153</v>
@@ -994,25 +994,25 @@
         <v>27</v>
       </c>
       <c r="D12" s="2">
-        <v>11153</v>
+        <v>10534</v>
       </c>
       <c r="E12" s="2">
-        <v>17447</v>
+        <v>20641</v>
       </c>
       <c r="F12" s="2">
-        <v>-6294</v>
+        <v>-10107</v>
       </c>
       <c r="G12" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H12" s="2">
         <v>30</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>15</v>
@@ -1026,16 +1026,16 @@
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D13" s="2">
         <v>11153</v>
       </c>
       <c r="E13" s="2">
-        <v>17447</v>
+        <v>20641</v>
       </c>
       <c r="F13" s="2">
-        <v>-6294</v>
+        <v>-9488</v>
       </c>
       <c r="G13" s="2">
         <v>30</v>
@@ -1046,8 +1046,8 @@
       <c r="I13" s="2">
         <v>0</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>14</v>
+      <c r="J13" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>15</v>
@@ -1055,22 +1055,22 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="D14" s="2">
         <v>11153</v>
       </c>
       <c r="E14" s="2">
-        <v>17447</v>
+        <v>20641</v>
       </c>
       <c r="F14" s="2">
-        <v>-6294</v>
+        <v>-9488</v>
       </c>
       <c r="G14" s="2">
         <v>30</v>
@@ -1081,8 +1081,8 @@
       <c r="I14" s="2">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>14</v>
+      <c r="J14" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>15</v>
@@ -1090,34 +1090,34 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D15" s="2">
-        <v>11153</v>
+        <v>10534</v>
       </c>
       <c r="E15" s="2">
         <v>17447</v>
       </c>
       <c r="F15" s="2">
-        <v>-6294</v>
+        <v>-6913</v>
       </c>
       <c r="G15" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H15" s="2">
         <v>30</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>15</v>
@@ -1125,13 +1125,13 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D16" s="2">
         <v>11153</v>
@@ -1160,22 +1160,22 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D17" s="2">
         <v>11153</v>
       </c>
       <c r="E17" s="2">
-        <v>20642</v>
+        <v>17447</v>
       </c>
       <c r="F17" s="2">
-        <v>-9489</v>
+        <v>-6294</v>
       </c>
       <c r="G17" s="2">
         <v>30</v>
@@ -1186,8 +1186,8 @@
       <c r="I17" s="2">
         <v>0</v>
       </c>
-      <c r="J17" s="5" t="s">
-        <v>32</v>
+      <c r="J17" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>15</v>
@@ -1195,34 +1195,34 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="D18" s="2">
-        <v>11153</v>
+        <v>10534</v>
       </c>
       <c r="E18" s="2">
-        <v>20642</v>
+        <v>20641</v>
       </c>
       <c r="F18" s="2">
-        <v>-9489</v>
+        <v>-10107</v>
       </c>
       <c r="G18" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H18" s="2">
         <v>30</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>15</v>
@@ -1230,22 +1230,22 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D19" s="2">
-        <v>11222</v>
+        <v>12218</v>
       </c>
       <c r="E19" s="2">
-        <v>20642</v>
+        <v>20641</v>
       </c>
       <c r="F19" s="2">
-        <v>-9420</v>
+        <v>-8423</v>
       </c>
       <c r="G19" s="2">
         <v>30</v>
@@ -1257,7 +1257,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>15</v>
@@ -1265,22 +1265,22 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D20" s="2">
-        <v>13693</v>
+        <v>12218</v>
       </c>
       <c r="E20" s="2">
-        <v>17447</v>
+        <v>20641</v>
       </c>
       <c r="F20" s="2">
-        <v>-3754</v>
+        <v>-8423</v>
       </c>
       <c r="G20" s="2">
         <v>30</v>
@@ -1291,8 +1291,8 @@
       <c r="I20" s="2">
         <v>0</v>
       </c>
-      <c r="J20" s="4" t="s">
-        <v>20</v>
+      <c r="J20" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>15</v>
@@ -1300,22 +1300,22 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D21" s="2">
-        <v>13693</v>
+        <v>13692</v>
       </c>
       <c r="E21" s="2">
         <v>17447</v>
       </c>
       <c r="F21" s="2">
-        <v>-3754</v>
+        <v>-3755</v>
       </c>
       <c r="G21" s="2">
         <v>30</v>
@@ -1327,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>15</v>
@@ -1335,22 +1335,22 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D22" s="2">
-        <v>13693</v>
+        <v>13692</v>
       </c>
       <c r="E22" s="2">
         <v>17447</v>
       </c>
       <c r="F22" s="2">
-        <v>-3754</v>
+        <v>-3755</v>
       </c>
       <c r="G22" s="2">
         <v>30</v>
@@ -1362,7 +1362,7 @@
         <v>0</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>15</v>
@@ -1370,22 +1370,22 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="D23" s="2">
-        <v>13693</v>
+        <v>13692</v>
       </c>
       <c r="E23" s="2">
-        <v>20642</v>
+        <v>17447</v>
       </c>
       <c r="F23" s="2">
-        <v>-6949</v>
+        <v>-3755</v>
       </c>
       <c r="G23" s="2">
         <v>30</v>
@@ -1396,8 +1396,8 @@
       <c r="I23" s="2">
         <v>0</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>14</v>
+      <c r="J23" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>15</v>
@@ -1405,19 +1405,19 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D24" s="2">
-        <v>13693</v>
+        <v>13692</v>
       </c>
       <c r="E24" s="2">
-        <v>20642</v>
+        <v>20641</v>
       </c>
       <c r="F24" s="2">
         <v>-6949</v>
@@ -1440,19 +1440,19 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="D25" s="2">
-        <v>13693</v>
+        <v>13692</v>
       </c>
       <c r="E25" s="2">
-        <v>20642</v>
+        <v>20641</v>
       </c>
       <c r="F25" s="2">
         <v>-6949</v>
@@ -1475,22 +1475,22 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D26" s="2">
-        <v>12218</v>
+        <v>13692</v>
       </c>
       <c r="E26" s="2">
-        <v>17447</v>
+        <v>20641</v>
       </c>
       <c r="F26" s="2">
-        <v>-5229</v>
+        <v>-6949</v>
       </c>
       <c r="G26" s="2">
         <v>30</v>
@@ -1501,8 +1501,8 @@
       <c r="I26" s="2">
         <v>0</v>
       </c>
-      <c r="J26" s="4" t="s">
-        <v>20</v>
+      <c r="J26" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>15</v>
@@ -1516,7 +1516,7 @@
         <v>12</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D27" s="2">
         <v>12218</v>
@@ -1537,7 +1537,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>15</v>
@@ -1551,16 +1551,16 @@
         <v>12</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D28" s="2">
-        <v>12464</v>
+        <v>12218</v>
       </c>
       <c r="E28" s="2">
         <v>17447</v>
       </c>
       <c r="F28" s="2">
-        <v>-4983</v>
+        <v>-5229</v>
       </c>
       <c r="G28" s="2">
         <v>30</v>
@@ -1572,7 +1572,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>15</v>
@@ -1580,22 +1580,22 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D29" s="2">
-        <v>11222</v>
+        <v>12464</v>
       </c>
       <c r="E29" s="2">
         <v>17447</v>
       </c>
       <c r="F29" s="2">
-        <v>-6225</v>
+        <v>-4983</v>
       </c>
       <c r="G29" s="2">
         <v>30</v>
@@ -1606,8 +1606,8 @@
       <c r="I29" s="2">
         <v>0</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>14</v>
+      <c r="J29" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>15</v>
@@ -1624,13 +1624,13 @@
         <v>13</v>
       </c>
       <c r="D30" s="2">
-        <v>12218</v>
+        <v>11221</v>
       </c>
       <c r="E30" s="2">
         <v>17447</v>
       </c>
       <c r="F30" s="2">
-        <v>-5229</v>
+        <v>-6226</v>
       </c>
       <c r="G30" s="2">
         <v>30</v>
@@ -1641,8 +1641,8 @@
       <c r="I30" s="2">
         <v>0</v>
       </c>
-      <c r="J30" s="4" t="s">
-        <v>20</v>
+      <c r="J30" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>15</v>
@@ -1656,7 +1656,7 @@
         <v>12</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D31" s="2">
         <v>12218</v>
@@ -1677,7 +1677,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>15</v>
@@ -1685,34 +1685,34 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D32" s="2">
-        <v>9816</v>
+        <v>12218</v>
       </c>
       <c r="E32" s="2">
         <v>17447</v>
       </c>
       <c r="F32" s="2">
-        <v>-7631</v>
+        <v>-5229</v>
       </c>
       <c r="G32" s="2">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H32" s="2">
         <v>30</v>
       </c>
       <c r="I32" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>15</v>
@@ -1726,16 +1726,16 @@
         <v>12</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D33" s="2">
-        <v>9816</v>
+        <v>9815</v>
       </c>
       <c r="E33" s="2">
         <v>17447</v>
       </c>
       <c r="F33" s="2">
-        <v>-7631</v>
+        <v>-7632</v>
       </c>
       <c r="G33" s="2">
         <v>15</v>
@@ -1747,7 +1747,7 @@
         <v>15</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>15</v>
@@ -1761,16 +1761,16 @@
         <v>12</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D34" s="2">
-        <v>10635</v>
+        <v>10634</v>
       </c>
       <c r="E34" s="2">
         <v>17447</v>
       </c>
       <c r="F34" s="2">
-        <v>-6812</v>
+        <v>-6813</v>
       </c>
       <c r="G34" s="2">
         <v>15</v>
@@ -1782,7 +1782,7 @@
         <v>15</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>15</v>
@@ -1790,7 +1790,7 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>12</v>
@@ -1799,25 +1799,25 @@
         <v>41</v>
       </c>
       <c r="D35" s="2">
-        <v>9816</v>
+        <v>13228</v>
       </c>
       <c r="E35" s="2">
-        <v>15044</v>
+        <v>17447</v>
       </c>
       <c r="F35" s="2">
-        <v>-5228</v>
+        <v>-4219</v>
       </c>
       <c r="G35" s="2">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H35" s="2">
         <v>30</v>
       </c>
       <c r="I35" s="2">
-        <v>15</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>20</v>
+        <v>-10</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>15</v>
@@ -1831,16 +1831,16 @@
         <v>12</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D36" s="2">
-        <v>9816</v>
+        <v>9815</v>
       </c>
       <c r="E36" s="2">
         <v>15044</v>
       </c>
       <c r="F36" s="2">
-        <v>-5228</v>
+        <v>-5229</v>
       </c>
       <c r="G36" s="2">
         <v>15</v>
@@ -1852,7 +1852,7 @@
         <v>15</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>15</v>
@@ -1866,16 +1866,16 @@
         <v>12</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D37" s="2">
-        <v>9816</v>
+        <v>9815</v>
       </c>
       <c r="E37" s="2">
         <v>15044</v>
       </c>
       <c r="F37" s="2">
-        <v>-5228</v>
+        <v>-5229</v>
       </c>
       <c r="G37" s="2">
         <v>15</v>
@@ -1887,7 +1887,7 @@
         <v>15</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>15</v>
@@ -1895,34 +1895,34 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D38" s="2">
-        <v>10662</v>
+        <v>9815</v>
       </c>
       <c r="E38" s="2">
-        <v>11863</v>
+        <v>15044</v>
       </c>
       <c r="F38" s="2">
-        <v>-1201</v>
+        <v>-5229</v>
       </c>
       <c r="G38" s="2">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H38" s="2">
         <v>30</v>
       </c>
       <c r="I38" s="2">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>15</v>
@@ -1936,16 +1936,16 @@
         <v>12</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D39" s="2">
-        <v>10894</v>
+        <v>10662</v>
       </c>
       <c r="E39" s="2">
         <v>11863</v>
       </c>
       <c r="F39" s="2">
-        <v>-969</v>
+        <v>-1201</v>
       </c>
       <c r="G39" s="2">
         <v>46</v>
@@ -1957,7 +1957,7 @@
         <v>-16</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>15</v>
@@ -1965,22 +1965,22 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D40" s="2">
-        <v>10662</v>
+        <v>10894</v>
       </c>
       <c r="E40" s="2">
-        <v>15044</v>
+        <v>11863</v>
       </c>
       <c r="F40" s="2">
-        <v>-4382</v>
+        <v>-969</v>
       </c>
       <c r="G40" s="2">
         <v>46</v>
@@ -1991,8 +1991,8 @@
       <c r="I40" s="2">
         <v>-16</v>
       </c>
-      <c r="J40" s="3" t="s">
-        <v>14</v>
+      <c r="J40" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>15</v>
@@ -2006,16 +2006,16 @@
         <v>12</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D41" s="2">
-        <v>10894</v>
+        <v>10662</v>
       </c>
       <c r="E41" s="2">
         <v>15044</v>
       </c>
       <c r="F41" s="2">
-        <v>-4150</v>
+        <v>-4382</v>
       </c>
       <c r="G41" s="2">
         <v>46</v>
@@ -2041,16 +2041,16 @@
         <v>12</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D42" s="2">
-        <v>11850</v>
+        <v>10894</v>
       </c>
       <c r="E42" s="2">
         <v>15044</v>
       </c>
       <c r="F42" s="2">
-        <v>-3194</v>
+        <v>-4150</v>
       </c>
       <c r="G42" s="2">
         <v>46</v>
@@ -2070,22 +2070,22 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D43" s="2">
-        <v>8068</v>
+        <v>11849</v>
       </c>
       <c r="E43" s="2">
         <v>15044</v>
       </c>
       <c r="F43" s="2">
-        <v>-6976</v>
+        <v>-3195</v>
       </c>
       <c r="G43" s="2">
         <v>46</v>
@@ -2096,8 +2096,8 @@
       <c r="I43" s="2">
         <v>-16</v>
       </c>
-      <c r="J43" s="5" t="s">
-        <v>32</v>
+      <c r="J43" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>15</v>
@@ -2111,16 +2111,16 @@
         <v>12</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D44" s="2">
-        <v>8300</v>
+        <v>8068</v>
       </c>
       <c r="E44" s="2">
         <v>15044</v>
       </c>
       <c r="F44" s="2">
-        <v>-6744</v>
+        <v>-6976</v>
       </c>
       <c r="G44" s="2">
         <v>46</v>
@@ -2132,7 +2132,7 @@
         <v>-16</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>15</v>
@@ -2146,16 +2146,16 @@
         <v>12</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D45" s="2">
-        <v>9269</v>
+        <v>8300</v>
       </c>
       <c r="E45" s="2">
         <v>15044</v>
       </c>
       <c r="F45" s="2">
-        <v>-5775</v>
+        <v>-6744</v>
       </c>
       <c r="G45" s="2">
         <v>46</v>
@@ -2166,8 +2166,8 @@
       <c r="I45" s="2">
         <v>-16</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>14</v>
+      <c r="J45" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>15</v>
@@ -2175,22 +2175,22 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D46" s="2">
-        <v>7495</v>
+        <v>9269</v>
       </c>
       <c r="E46" s="2">
-        <v>8382</v>
+        <v>15044</v>
       </c>
       <c r="F46" s="2">
-        <v>-887</v>
+        <v>-5775</v>
       </c>
       <c r="G46" s="2">
         <v>46</v>
@@ -2201,8 +2201,8 @@
       <c r="I46" s="2">
         <v>-16</v>
       </c>
-      <c r="J46" s="4" t="s">
-        <v>20</v>
+      <c r="J46" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>15</v>
@@ -2210,22 +2210,22 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D47" s="2">
-        <v>8068</v>
+        <v>7494</v>
       </c>
       <c r="E47" s="2">
-        <v>9856</v>
+        <v>8382</v>
       </c>
       <c r="F47" s="2">
-        <v>-1788</v>
+        <v>-888</v>
       </c>
       <c r="G47" s="2">
         <v>46</v>
@@ -2237,7 +2237,7 @@
         <v>-16</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>15</v>
@@ -2251,16 +2251,16 @@
         <v>12</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D48" s="2">
-        <v>9269</v>
+        <v>8068</v>
       </c>
       <c r="E48" s="2">
         <v>9856</v>
       </c>
       <c r="F48" s="2">
-        <v>-587</v>
+        <v>-1788</v>
       </c>
       <c r="G48" s="2">
         <v>46</v>
@@ -2272,9 +2272,44 @@
         <v>-16</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K48" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D49" s="2">
+        <v>9269</v>
+      </c>
+      <c r="E49" s="2">
+        <v>9856</v>
+      </c>
+      <c r="F49" s="2">
+        <v>-587</v>
+      </c>
+      <c r="G49" s="2">
+        <v>46</v>
+      </c>
+      <c r="H49" s="2">
+        <v>30</v>
+      </c>
+      <c r="I49" s="2">
+        <v>-16</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K49" s="2" t="s">
         <v>15</v>
       </c>
     </row>
